--- a/request_forms/021_table_saw_extension_request_form--request_forms.xlsx
+++ b/request_forms/021_table_saw_extension_request_form--request_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>equipment_id</t>
+          <t>equipment_id_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Equipment Id</t>
+          <t>Equipment Id 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>workshop_name</t>
+          <t>workshop_name_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Workshop Name</t>
+          <t>Workshop Name 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Supervisor Approval</t>
+          <t>Supervisor Approval2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1217,8 +1217,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="27" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1246,12 +1246,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'approved'}</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Approved'}</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -1263,12 +1263,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'denied'}</t>
+          <t>denied</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Denied'}</t>
+          <t>Denied</t>
         </is>
       </c>
     </row>
@@ -1280,12 +1280,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Pending'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1297,12 +1297,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'available'}</t>
+          <t>available</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Available'}</t>
+          <t>Available</t>
         </is>
       </c>
     </row>
@@ -1314,12 +1314,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'in_use'}</t>
+          <t>in_use</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'In Use'}</t>
+          <t>In Use</t>
         </is>
       </c>
     </row>
@@ -1331,12 +1331,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'maintenance'}</t>
+          <t>maintenance</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Maintenance'}</t>
+          <t>Maintenance</t>
         </is>
       </c>
     </row>
@@ -1348,12 +1348,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'out_of_order'}</t>
+          <t>out_of_order</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Out of Order'}</t>
+          <t>Out of Order</t>
         </is>
       </c>
     </row>
@@ -1365,12 +1365,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'approved'}</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Approved'}</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -1382,12 +1382,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'denied'}</t>
+          <t>denied</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Denied'}</t>
+          <t>Denied</t>
         </is>
       </c>
     </row>
@@ -1399,12 +1399,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Pending'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
